--- a/excel_routes/route_HMB_TUU_threats.xlsx
+++ b/excel_routes/route_HMB_TUU_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -86,9 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,12 +447,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -546,13 +537,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6875</v>
+        <v>6978</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>11226</v>
+        <v>11367</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4351</v>
+        <v>-4389</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -591,13 +582,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11379</v>
+        <v>11239</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>14196</v>
+        <v>14354</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-2817</v>
+        <v>-3115</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -622,7 +613,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,30 +623,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9001</v>
+        <v>6738</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>18547</v>
+        <v>10602</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-9546</v>
+        <v>-3864</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +658,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,17 +668,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12536</v>
+        <v>6978</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>18547</v>
+        <v>10602</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-6011</v>
+        <v>-3624</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -698,597 +689,12 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SM-327</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-307</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>12704</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>18547</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>-5843</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>SM-327</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-107</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>12704</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>18547</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>-5843</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>31-JUL-26</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SM-327</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-120</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>12536</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>17166</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-4630</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>31-JUL-26</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SM-327</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-307</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>12704</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>17166</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-4462</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>31-JUL-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-327</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-107</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>12704</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>17166</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-4462</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>21-AUG-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-327</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-307</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>12704</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>16176</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-3472</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>04-SEP-26</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SM-327</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-307</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>11072</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>17166</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-6094</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>04-SEP-26</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SM-327</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-107</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>11072</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>17166</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>-6094</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>11-SEP-26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SM-327</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-307</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>11072</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>17166</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-6094</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>11-SEP-26</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>SM-327</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-107</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>11072</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>17166</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-6094</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>SM-327</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-599</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>9001</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>17166</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>-8165</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-327</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-307</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>11072</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>17166</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-6094</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>SM-327</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-107</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>11072</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>17166</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-6094</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_TUU_threats.xlsx
+++ b/excel_routes/route_HMB_TUU_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -540,10 +540,10 @@
         <v>6978</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>11367</v>
+        <v>9824</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4389</v>
+        <v>-2846</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -605,96 +605,6 @@
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>12-JUN-26</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>SM-327</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-120</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>6738</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>10602</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>-3864</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>12-JUN-26</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>SM-327</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-307</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>6978</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>10602</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>-3624</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_TUU_threats.xlsx
+++ b/excel_routes/route_HMB_TUU_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +86,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,12 +456,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -537,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6978</v>
+        <v>6947</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9824</v>
+        <v>10569</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-2846</v>
+        <v>-3622</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -568,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -578,33 +587,303 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>9009</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>13345</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>-4336</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-120</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>12655</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>18729</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-6074</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>Nile Air NP-307</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>11239</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>14354</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>-3115</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I3" s="2" t="n">
+      <c r="D5" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>18729</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-5891</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>18729</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-5891</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-120</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>12655</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>17333</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-4678</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>17333</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-4495</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>17333</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-4495</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_TUU_threats.xlsx
+++ b/excel_routes/route_HMB_TUU_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -549,10 +549,10 @@
         <v>6947</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10569</v>
+        <v>10583</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3622</v>
+        <v>-3636</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,26 +587,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>9009</v>
+        <v>11189</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13345</v>
+        <v>14346</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4336</v>
+        <v>-3157</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -632,26 +632,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>12655</v>
+        <v>9012</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-6074</v>
+        <v>-9717</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12838</v>
+        <v>12669</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-5891</v>
+        <v>-6060</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,17 +767,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12655</v>
+        <v>11189</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>17333</v>
+        <v>17347</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-4678</v>
+        <v>-6158</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -788,9 +788,9 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,17 +812,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12838</v>
+        <v>11189</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>17333</v>
+        <v>17347</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-4495</v>
+        <v>-6158</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -833,9 +833,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>12838</v>
+        <v>11189</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>17333</v>
+        <v>17347</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-4495</v>
+        <v>-6158</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -878,12 +878,192 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>17347</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-6158</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>9012</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>17347</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-8335</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>17347</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-6158</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>17347</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-6158</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_TUU_threats.xlsx
+++ b/excel_routes/route_HMB_TUU_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -622,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,30 +632,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9012</v>
+        <v>7412</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>18729</v>
+        <v>10583</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-9717</v>
+        <v>-3171</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,30 +677,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12669</v>
+        <v>9012</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>18729</v>
+        <v>13345</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-6060</v>
+        <v>-4333</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -722,26 +722,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>12838</v>
+        <v>9012</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-5891</v>
+        <v>-9717</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,17 +767,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>11189</v>
+        <v>12669</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>17347</v>
+        <v>18729</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-6158</v>
+        <v>-6060</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,17 +812,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>11189</v>
+        <v>12838</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>17347</v>
+        <v>18729</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-6158</v>
+        <v>-5891</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>11189</v>
+        <v>12669</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>17347</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-6158</v>
+        <v>-4678</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -878,9 +878,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>11189</v>
+        <v>12838</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>17347</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-6158</v>
+        <v>-4509</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -923,9 +923,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,30 +947,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>9012</v>
+        <v>12838</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>17347</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-8335</v>
+        <v>-4509</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1064,6 +1064,231 @@
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>17347</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-6158</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>17347</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-6158</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>9012</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>17347</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-8335</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>17347</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-6158</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>17347</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-6158</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_TUU_threats.xlsx
+++ b/excel_routes/route_HMB_TUU_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9012</v>
+        <v>9008</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13345</v>
+        <v>18729</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-4333</v>
+        <v>-9721</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>20</v>
@@ -698,9 +698,9 @@
       <c r="I5" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -722,26 +722,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9012</v>
+        <v>12669</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-9717</v>
+        <v>-6060</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -767,17 +767,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12669</v>
+        <v>12838</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-6060</v>
+        <v>-5891</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,17 +812,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12838</v>
+        <v>12669</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>18729</v>
+        <v>17347</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-5891</v>
+        <v>-4678</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -833,9 +833,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>12669</v>
+        <v>12838</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>17347</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-4678</v>
+        <v>-4509</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>12838</v>
+        <v>11189</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>17347</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-4509</v>
+        <v>-6158</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -968,9 +968,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>18-SEP-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,26 +1127,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>11189</v>
+        <v>9008</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>17347</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-6158</v>
+        <v>-8339</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1172,26 +1172,26 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9012</v>
+        <v>11189</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>17347</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-8335</v>
+        <v>-6158</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
@@ -1244,51 +1244,6 @@
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>SM-327</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-107</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>11189</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>17347</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-6158</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_TUU_threats.xlsx
+++ b/excel_routes/route_HMB_TUU_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6947</v>
+        <v>10177</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10583</v>
+        <v>13319</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3636</v>
+        <v>-3142</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -587,17 +587,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11189</v>
+        <v>10177</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>14346</v>
+        <v>13319</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-3157</v>
+        <v>-3142</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -636,13 +636,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7412</v>
+        <v>6687</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10583</v>
+        <v>10540</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3171</v>
+        <v>-3853</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,30 +677,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9008</v>
+        <v>6924</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>18729</v>
+        <v>10540</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-9721</v>
+        <v>-3616</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>12669</v>
+        <v>6924</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>18729</v>
+        <v>10540</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-6060</v>
+        <v>-3616</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -743,9 +743,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,30 +767,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12838</v>
+        <v>8935</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>18729</v>
+        <v>13319</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-5891</v>
+        <v>-4384</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12669</v>
+        <v>9689</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>17347</v>
+        <v>13319</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-4678</v>
+        <v>-3630</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,30 +857,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>12838</v>
+        <v>8935</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>17347</v>
+        <v>18722</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-4509</v>
+        <v>-9787</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>12838</v>
+        <v>12649</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>17347</v>
+        <v>18722</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-4509</v>
+        <v>-6073</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -923,9 +923,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>11189</v>
+        <v>12788</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>17347</v>
+        <v>18722</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-6158</v>
+        <v>-5934</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -982,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>11189</v>
+        <v>12649</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>17347</v>
+        <v>17340</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-6158</v>
+        <v>-4691</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1013,9 +1013,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1041,13 +1041,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>11189</v>
+        <v>12788</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>17347</v>
+        <v>17340</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-6158</v>
+        <v>-4552</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1058,9 +1058,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1086,13 +1086,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>11189</v>
+        <v>12788</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>17347</v>
+        <v>17340</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-6158</v>
+        <v>-4552</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1103,9 +1103,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,30 +1127,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9008</v>
+        <v>12788</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>17347</v>
+        <v>16334</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-8339</v>
+        <v>-3546</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>11189</v>
+        <v>11155</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>17347</v>
+        <v>17340</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-6158</v>
+        <v>-6185</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1207,43 +1207,133 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>04-SEP-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>11155</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>17340</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-6185</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>18-SEP-26</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-327</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>11155</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>17340</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-6185</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Nile Air NP-107</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
-        <v>11189</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>17347</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-6158</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="D19" s="2" t="n">
+        <v>11155</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>17340</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-6185</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_TUU_threats.xlsx
+++ b/excel_routes/route_HMB_TUU_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,12 @@
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -546,13 +555,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10177</v>
+        <v>8956</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13319</v>
+        <v>13206</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3142</v>
+        <v>-4250</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -577,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -591,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10177</v>
+        <v>8956</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13319</v>
+        <v>13206</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-3142</v>
+        <v>-4250</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -622,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -636,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6687</v>
+        <v>9591</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10540</v>
+        <v>13206</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3853</v>
+        <v>-3615</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -667,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6924</v>
+        <v>8839</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>10540</v>
+        <v>18575</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-3616</v>
+        <v>-9736</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -712,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6924</v>
+        <v>8956</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>10540</v>
+        <v>18575</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-3616</v>
+        <v>-9619</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -743,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -757,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8935</v>
+        <v>8956</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>13319</v>
+        <v>18575</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-4384</v>
+        <v>-9619</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -816,13 +825,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>9689</v>
+        <v>12530</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>13319</v>
+        <v>17195</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-3630</v>
+        <v>-4665</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -847,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8935</v>
+        <v>12668</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>18722</v>
+        <v>17195</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-9787</v>
+        <v>-4527</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -892,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>12649</v>
+        <v>12668</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>18722</v>
+        <v>17195</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-6073</v>
+        <v>-4527</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -923,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -937,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>12788</v>
+        <v>12668</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>18722</v>
+        <v>16201</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-5934</v>
+        <v>-3533</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -968,9 +977,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -982,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>12649</v>
+        <v>11026</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>17340</v>
+        <v>17195</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-4691</v>
+        <v>-6169</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1013,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1027,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>12788</v>
+        <v>11026</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>17340</v>
+        <v>17195</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-4552</v>
+        <v>-6169</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1058,9 +1067,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1072,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>12788</v>
+        <v>11095</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>17340</v>
+        <v>17195</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-4552</v>
+        <v>-6100</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1103,9 +1112,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1117,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>12788</v>
+        <v>11026</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16334</v>
+        <v>17195</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-3546</v>
+        <v>-6169</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1148,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1162,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>11155</v>
+        <v>11026</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>17340</v>
+        <v>17195</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-6185</v>
+        <v>-6169</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1207,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1217,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>11155</v>
+        <v>11095</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>17340</v>
+        <v>17195</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-6185</v>
+        <v>-6100</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1262,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>11155</v>
+        <v>8838</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>17340</v>
+        <v>17195</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-6185</v>
+        <v>-8357</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -1307,33 +1316,78 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>11026</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>17195</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-6169</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
           <t>Nile Air NP-107</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
-        <v>11155</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>17340</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-6185</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="D20" s="2" t="n">
+        <v>11026</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>17195</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-6169</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
